--- a/NECP Scenario/Results/Regional Results/EL65_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL65_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547326808097899E-12</v>
+        <v>2.284567441279966E-12</v>
       </c>
       <c r="C2">
-        <v>8.102407200508812E-13</v>
+        <v>1.196287064785645E-12</v>
       </c>
       <c r="D2">
-        <v>1.190477468576128E-12</v>
+        <v>1.757694710023283E-12</v>
       </c>
       <c r="E2">
-        <v>1.749238753247051E-12</v>
+        <v>2.58268457101296E-12</v>
       </c>
       <c r="F2">
-        <v>2.570230953999656E-12</v>
+        <v>3.794847108309497E-12</v>
       </c>
       <c r="G2">
-        <v>3.776469385018638E-12</v>
+        <v>5.575811442192874E-12</v>
       </c>
       <c r="H2">
-        <v>2.288778520798417E-11</v>
+        <v>3.379309588832442E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.512595133557792E-08</v>
+        <v>8.082524692162775E-08</v>
       </c>
       <c r="C3">
-        <v>4.585383214257948E-08</v>
+        <v>6.793081867355957E-08</v>
       </c>
       <c r="D3">
-        <v>1.333670679983268E-07</v>
+        <v>1.954414563453678E-07</v>
       </c>
       <c r="E3">
-        <v>2.770556708560911E-07</v>
+        <v>3.908163935183456E-07</v>
       </c>
       <c r="F3">
-        <v>9.097542921434257E-07</v>
+        <v>1.307198305226602E-06</v>
       </c>
       <c r="G3">
-        <v>8.209193190921054E-06</v>
+        <v>0.02833913376591214</v>
       </c>
       <c r="H3">
-        <v>2.001528742022552</v>
+        <v>1.604954997142209</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.685705863800078E-08</v>
+        <v>6.870145988573584E-08</v>
       </c>
       <c r="C4">
-        <v>3.897575732698052E-08</v>
+        <v>5.77411958763112E-08</v>
       </c>
       <c r="D4">
-        <v>1.133620078044029E-07</v>
+        <v>1.661252378973751E-07</v>
       </c>
       <c r="E4">
-        <v>2.354973202335706E-07</v>
+        <v>3.321939344944592E-07</v>
       </c>
       <c r="F4">
-        <v>7.732911483277736E-07</v>
+        <v>1.111118559446454E-06</v>
       </c>
       <c r="G4">
-        <v>6.977814212289211E-06</v>
+        <v>0.02408826370102502</v>
       </c>
       <c r="H4">
-        <v>1.701299430720958</v>
+        <v>1.364211747570851</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.308072663751624</v>
+        <v>0.308067833019894</v>
       </c>
       <c r="D5">
-        <v>0.3051370395374333</v>
+        <v>0.3050661683499217</v>
       </c>
       <c r="E5">
-        <v>0.3306400962224985</v>
+        <v>0.3305066326998731</v>
       </c>
       <c r="F5">
-        <v>0.350075225310937</v>
+        <v>0.3501596614936219</v>
       </c>
       <c r="G5">
-        <v>0.3644247032929117</v>
+        <v>0.3644422421589981</v>
       </c>
       <c r="H5">
-        <v>0.3793695074739638</v>
+        <v>0.3795831169490232</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.03701412018907332</v>
+        <v>0.03705789877140948</v>
       </c>
       <c r="C7">
-        <v>0.9172777772724932</v>
+        <v>0.9172777765886665</v>
       </c>
       <c r="D7">
-        <v>0.9047760981669422</v>
+        <v>0.9045556327518119</v>
       </c>
       <c r="E7">
-        <v>0.9765138893168933</v>
+        <v>0.9765138891692474</v>
       </c>
       <c r="F7">
-        <v>1.030500000555482</v>
+        <v>1.030500000429528</v>
       </c>
       <c r="G7">
-        <v>1.069375000383827</v>
+        <v>1.069375000165087</v>
       </c>
       <c r="H7">
-        <v>1.108249997919674</v>
+        <v>1.108249996906921</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.01294200006238018</v>
+        <v>0.01295730725722565</v>
       </c>
       <c r="C9">
-        <v>0.01265383179628112</v>
+        <v>0.01265866228795732</v>
       </c>
       <c r="D9">
-        <v>0.0112182395390407</v>
+        <v>0.01121202491571409</v>
       </c>
       <c r="E9">
-        <v>0.01079832661135747</v>
+        <v>0.01093179008036074</v>
       </c>
       <c r="F9">
-        <v>0.01023946019178843</v>
+        <v>0.01015502396211688</v>
       </c>
       <c r="G9">
-        <v>0.009482639489550387</v>
+        <v>0.009465100542644302</v>
       </c>
       <c r="H9">
-        <v>0.008130491743560087</v>
+        <v>0.007916881888133033</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>8.328287253943018E-08</v>
+        <v>1.204874500510657E-07</v>
       </c>
       <c r="D10">
-        <v>8.78857568434613E-08</v>
+        <v>1.326642698928455E-07</v>
       </c>
       <c r="E10">
-        <v>8.498927881021769E-08</v>
+        <v>1.266148157249421E-07</v>
       </c>
       <c r="F10">
-        <v>6.874539422088439E-08</v>
+        <v>1.020071747226913E-07</v>
       </c>
       <c r="G10">
-        <v>6.408235766625492E-08</v>
+        <v>9.520367366939087E-08</v>
       </c>
       <c r="H10">
-        <v>4.393016064893555E-07</v>
+        <v>6.641719328330311E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -771,22 +771,22 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.97793402696724</v>
+        <v>4.000495543101265</v>
       </c>
       <c r="C11">
-        <v>4.431859091837416</v>
+        <v>4.155074099668452</v>
       </c>
       <c r="D11">
-        <v>4.281154746533751</v>
+        <v>4.131823226002135</v>
       </c>
       <c r="E11">
-        <v>3.915864076681525</v>
+        <v>3.874353994493482</v>
       </c>
       <c r="F11">
-        <v>3.410221349456738</v>
+        <v>3.389526723383313</v>
       </c>
       <c r="G11">
-        <v>2.163651179338189</v>
+        <v>2.163945966682556</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.1997417121161263</v>
+        <v>0.1733510223839038</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.06658056882951806</v>
+        <v>0.05778367137657672</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.765529818817282</v>
+        <v>2.765529821276959</v>
       </c>
       <c r="C14">
-        <v>2.809502710258449</v>
+        <v>2.809502708460007</v>
       </c>
       <c r="D14">
-        <v>3.089365366264782</v>
+        <v>3.089365356252412</v>
       </c>
       <c r="E14">
-        <v>3.689797954450521</v>
+        <v>3.689797920715334</v>
       </c>
       <c r="F14">
-        <v>4.468324866965316</v>
+        <v>4.468324733052789</v>
       </c>
       <c r="G14">
-        <v>5.123958070137522</v>
+        <v>4.562415226385117</v>
       </c>
       <c r="H14">
-        <v>5.895579542954517</v>
+        <v>5.895579768984127</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.669083172848108E-08</v>
+        <v>6.840985965196469E-08</v>
       </c>
       <c r="C19">
-        <v>4.256121088905537E-08</v>
+        <v>6.311436976341234E-08</v>
       </c>
       <c r="D19">
-        <v>1.026201257523551E-07</v>
+        <v>1.518011899045049E-07</v>
       </c>
       <c r="E19">
-        <v>2.229509864674941E-07</v>
+        <v>3.193408344247153E-07</v>
       </c>
       <c r="F19">
-        <v>6.252834578012915E-07</v>
+        <v>9.095255008847684E-07</v>
       </c>
       <c r="G19">
-        <v>1.194881139037657E-06</v>
+        <v>2.073991753275952E-06</v>
       </c>
       <c r="H19">
-        <v>1.125824992909477E-05</v>
+        <v>2.32054054580834E-05</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.735266538679704E-08</v>
+        <v>5.472788772518435E-08</v>
       </c>
       <c r="C21">
-        <v>3.404896871124429E-08</v>
+        <v>5.049149581072983E-08</v>
       </c>
       <c r="D21">
-        <v>8.209610060188408E-08</v>
+        <v>1.214409519236039E-07</v>
       </c>
       <c r="E21">
-        <v>1.783607891739952E-07</v>
+        <v>2.554726675397722E-07</v>
       </c>
       <c r="F21">
-        <v>5.002267662410327E-07</v>
+        <v>7.276204007078147E-07</v>
       </c>
       <c r="G21">
-        <v>9.559049112301257E-07</v>
+        <v>1.659193402620762E-06</v>
       </c>
       <c r="H21">
-        <v>9.006599943275824E-06</v>
+        <v>1.856432436646675E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.487991485993589E-08</v>
+        <v>2.182418017093473E-08</v>
       </c>
       <c r="D22">
-        <v>2.133911875074299E-08</v>
+        <v>3.238247093232113E-08</v>
       </c>
       <c r="E22">
-        <v>4.781710178108057E-08</v>
+        <v>7.117833795951745E-08</v>
       </c>
       <c r="F22">
-        <v>1.571878746859366E-07</v>
+        <v>2.414207937758485E-07</v>
       </c>
       <c r="G22">
-        <v>6.784085471041799E-07</v>
+        <v>1.436672970401323E-06</v>
       </c>
       <c r="H22">
-        <v>0.05806818722435907</v>
+        <v>0.05806818661261288</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.09524030589975577</v>
+        <v>0.09524030585841979</v>
       </c>
       <c r="C23">
-        <v>0.09524030593402262</v>
+        <v>0.0952403059088454</v>
       </c>
       <c r="D23">
-        <v>0.09524030590905687</v>
+        <v>0.09524030587210004</v>
       </c>
       <c r="E23">
-        <v>0.09524030589008993</v>
+        <v>0.09524030584363087</v>
       </c>
       <c r="F23">
-        <v>0.09524030586050176</v>
+        <v>0.09524030579962896</v>
       </c>
       <c r="G23">
-        <v>0.09524030579974101</v>
+        <v>0.09524030571123729</v>
       </c>
       <c r="H23">
-        <v>0.09524030474268315</v>
+        <v>0.0952403041687141</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>7.24608322484545</v>
+        <v>7.286191675858161</v>
       </c>
       <c r="C24">
-        <v>8.058332521941805</v>
+        <v>7.562887454850078</v>
       </c>
       <c r="D24">
-        <v>7.788571753785104</v>
+        <v>7.521268415001172</v>
       </c>
       <c r="E24">
-        <v>7.134701451621281</v>
+        <v>7.060398483061735</v>
       </c>
       <c r="F24">
-        <v>6.229600938236486</v>
+        <v>6.192557619871046</v>
       </c>
       <c r="G24">
-        <v>3.872935729488562</v>
+        <v>3.8734634562782</v>
       </c>
       <c r="H24">
-        <v>7.983009054045044E-07</v>
+        <v>1.20413368761513E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.585292771919263E-09</v>
+        <v>3.820620041701152E-09</v>
       </c>
       <c r="C25">
-        <v>2.222627069882906E-09</v>
+        <v>3.27659720857171E-09</v>
       </c>
       <c r="D25">
-        <v>2.602846819465786E-09</v>
+        <v>3.850241834307166E-09</v>
       </c>
       <c r="E25">
-        <v>3.466907082478959E-09</v>
+        <v>5.126795584383208E-09</v>
       </c>
       <c r="F25">
-        <v>3.868705283693797E-09</v>
+        <v>5.713269188627622E-09</v>
       </c>
       <c r="G25">
-        <v>4.550548208867698E-09</v>
+        <v>6.728534283766197E-09</v>
       </c>
       <c r="H25">
-        <v>2.781731981965616E-08</v>
+        <v>4.105485331487553E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.130314725118881E-08</v>
+        <v>1.657248749596455E-08</v>
       </c>
       <c r="D27">
-        <v>4.034211217707845E-08</v>
+        <v>5.934692679631503E-08</v>
       </c>
       <c r="E27">
-        <v>1.364330516640767E-07</v>
+        <v>1.932764484791952E-07</v>
       </c>
       <c r="F27">
-        <v>4.596844208533642E-07</v>
+        <v>6.089890439404616E-07</v>
       </c>
       <c r="G27">
-        <v>1.857366766377657E-06</v>
+        <v>2.33582009823469E-06</v>
       </c>
       <c r="H27">
-        <v>1.170606646017009</v>
+        <v>1.328597122795893</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.4245591243582464</v>
+        <v>0.2337814401000373</v>
       </c>
       <c r="D30">
-        <v>0.4724134023666934</v>
+        <v>0.3286319068138046</v>
       </c>
       <c r="E30">
-        <v>0.6467107609294246</v>
+        <v>0.4448810904707028</v>
       </c>
       <c r="F30">
-        <v>0.7206499543191716</v>
+        <v>0.4992346430071771</v>
       </c>
       <c r="G30">
-        <v>1.288949352520224</v>
+        <v>1.174569782636353</v>
       </c>
       <c r="H30">
-        <v>1.320703833549852</v>
+        <v>1.195175534742094</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.6391086522384054</v>
+        <v>0.6391086494930422</v>
       </c>
       <c r="C31">
-        <v>0.6386811842789641</v>
+        <v>0.6389903429821507</v>
       </c>
       <c r="D31">
-        <v>0.6383321727216785</v>
+        <v>0.6382149998248069</v>
       </c>
       <c r="E31">
-        <v>0.6321815376875475</v>
+        <v>0.6338838509394048</v>
       </c>
       <c r="F31">
-        <v>0.6253470032832037</v>
+        <v>0.6295758020893408</v>
       </c>
       <c r="G31">
-        <v>0.6016262259785128</v>
+        <v>0.6073551513757982</v>
       </c>
       <c r="H31">
-        <v>0.6271420765750492</v>
+        <v>0.6244232047320406</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>8.416101285963436E-09</v>
+        <v>1.242879216738521E-08</v>
       </c>
       <c r="D32">
-        <v>2.676900675715148E-08</v>
+        <v>4.166724242889829E-08</v>
       </c>
       <c r="E32">
-        <v>7.569047962776116E-08</v>
+        <v>1.170563179540113E-07</v>
       </c>
       <c r="F32">
-        <v>2.310802165604594E-07</v>
+        <v>3.778588276204944E-07</v>
       </c>
       <c r="G32">
-        <v>0.1737782178408959</v>
+        <v>0.7353210809277666</v>
       </c>
       <c r="H32">
-        <v>0.7353209211512053</v>
+        <v>0.7353208064424706</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.02983125037439505</v>
+        <v>0.02983124793255344</v>
       </c>
       <c r="C33">
-        <v>0.02983125120993825</v>
+        <v>0.02983124900760378</v>
       </c>
       <c r="D33">
-        <v>0.02983124515047135</v>
+        <v>0.02983124027433243</v>
       </c>
       <c r="E33">
-        <v>0.02983123995967241</v>
+        <v>0.02983123235143562</v>
       </c>
       <c r="F33">
-        <v>0.02983122976748034</v>
+        <v>0.02983121692327708</v>
       </c>
       <c r="G33">
-        <v>0.02983121323875539</v>
+        <v>0.02983119394758709</v>
       </c>
       <c r="H33">
-        <v>0.02983101605063514</v>
+        <v>0.02983090496330775</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>6.13787130269512E-09</v>
+        <v>9.038524303099201E-09</v>
       </c>
       <c r="D34">
-        <v>8.032504647329221E-09</v>
+        <v>1.199828286737894E-08</v>
       </c>
       <c r="E34">
-        <v>1.318589005898124E-08</v>
+        <v>1.954230658349653E-08</v>
       </c>
       <c r="F34">
-        <v>1.945911991271815E-08</v>
+        <v>2.882904379046098E-08</v>
       </c>
       <c r="G34">
-        <v>2.82257202328056E-08</v>
+        <v>4.144424230375272E-08</v>
       </c>
       <c r="H34">
-        <v>1.752307506338815E-07</v>
+        <v>2.650945670662721E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.006510138609800221</v>
+        <v>0.006510138603067499</v>
       </c>
       <c r="C35">
-        <v>0.006510135984491303</v>
+        <v>0.006510134671690608</v>
       </c>
       <c r="D35">
-        <v>0.006510132829133829</v>
+        <v>0.006510121983745709</v>
       </c>
       <c r="E35">
-        <v>0.006501285547716889</v>
+        <v>0.00650317789527868</v>
       </c>
       <c r="F35">
-        <v>0.006476784068434482</v>
+        <v>0.006490650065354631</v>
       </c>
       <c r="G35">
-        <v>0.006380318483339171</v>
+        <v>0.006396011501111697</v>
       </c>
       <c r="H35">
-        <v>0.00649381853810636</v>
+        <v>0.006476579071272624</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1.046331328350127E-07</v>
+        <v>1.495914364769688E-07</v>
       </c>
       <c r="D36">
-        <v>9.877411882082592E-08</v>
+        <v>1.408059727200085E-07</v>
       </c>
       <c r="E36">
-        <v>4.43728714510379E-07</v>
+        <v>5.965646762478994E-07</v>
       </c>
       <c r="F36">
-        <v>4.255990842832897E-07</v>
+        <v>5.76863534201552E-07</v>
       </c>
       <c r="G36">
-        <v>4.093929740418412E-07</v>
+        <v>5.580583314692561E-07</v>
       </c>
       <c r="H36">
-        <v>1.226452265669796E-06</v>
+        <v>1.738259248087684E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.376448791842318</v>
+        <v>0.3764487867558873</v>
       </c>
       <c r="C37">
-        <v>0.3549600975175432</v>
+        <v>0.3549792923078133</v>
       </c>
       <c r="D37">
-        <v>0.3362000880209102</v>
+        <v>0.3324248826306079</v>
       </c>
       <c r="E37">
-        <v>0.3200006943382079</v>
+        <v>0.3194918326685469</v>
       </c>
       <c r="F37">
-        <v>0.3190649643436321</v>
+        <v>0.3183535115159378</v>
       </c>
       <c r="G37">
-        <v>0.3145510114820601</v>
+        <v>0.3175487543084728</v>
       </c>
       <c r="H37">
-        <v>0.3411065030051488</v>
+        <v>0.335461930342926</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.0001328820406991722</v>
+        <v>0.0001328923210673537</v>
       </c>
       <c r="C38">
-        <v>0.02256055054792883</v>
+        <v>0.02187428867778391</v>
       </c>
       <c r="D38">
-        <v>0.04206160189759668</v>
+        <v>0.0460092747458713</v>
       </c>
       <c r="E38">
-        <v>0.07084442581513015</v>
+        <v>0.06755587049567503</v>
       </c>
       <c r="F38">
-        <v>0.08587831498860285</v>
+        <v>0.07730343538373145</v>
       </c>
       <c r="G38">
-        <v>0.1456386659151763</v>
+        <v>0.1284679295463023</v>
       </c>
       <c r="H38">
-        <v>0.657157590992884</v>
+        <v>0.825205655147169</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1.01816783064059E-07</v>
+        <v>1.492351065735925E-07</v>
       </c>
       <c r="C40">
-        <v>8.841504303163485E-08</v>
+        <v>1.310451884369719E-07</v>
       </c>
       <c r="D40">
-        <v>2.359871937506819E-07</v>
+        <v>3.472426462498726E-07</v>
       </c>
       <c r="E40">
-        <v>5.000066573235852E-07</v>
+        <v>7.101572279430609E-07</v>
       </c>
       <c r="F40">
-        <v>1.535037749944717E-06</v>
+        <v>2.21672380611137E-06</v>
       </c>
       <c r="G40">
-        <v>9.404074329958711E-06</v>
+        <v>0.02834120775766541</v>
       </c>
       <c r="H40">
-        <v>2.001540000272481</v>
+        <v>1.604978202547667</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.420972402479782E-08</v>
+        <v>1.234293476109202E-07</v>
       </c>
       <c r="C41">
-        <v>7.302472603822482E-08</v>
+        <v>1.08232691687041E-07</v>
       </c>
       <c r="D41">
-        <v>1.95458108406287E-07</v>
+        <v>2.87566189820979E-07</v>
       </c>
       <c r="E41">
-        <v>4.138581094075658E-07</v>
+        <v>5.876666020342314E-07</v>
       </c>
       <c r="F41">
-        <v>1.273517914568806E-06</v>
+        <v>1.838738960154269E-06</v>
       </c>
       <c r="G41">
-        <v>7.933719123519337E-06</v>
+        <v>0.02408992289442765</v>
       </c>
       <c r="H41">
-        <v>1.701308437320901</v>
+        <v>1.364230311895218</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.760705903926118E-08</v>
+        <v>-2.580575896267228E-08</v>
       </c>
       <c r="C42">
-        <v>-1.539031699341004E-08</v>
+        <v>-2.28124967499309E-08</v>
       </c>
       <c r="D42">
-        <v>-4.052908534439494E-08</v>
+        <v>-5.967645642889367E-08</v>
       </c>
       <c r="E42">
-        <v>-8.614854791601942E-08</v>
+        <v>-1.224906259088295E-07</v>
       </c>
       <c r="F42">
-        <v>-2.615198353759107E-07</v>
+        <v>-3.779848459571013E-07</v>
       </c>
       <c r="G42">
-        <v>-1.470355206439374E-06</v>
+        <v>-0.004251284863237767</v>
       </c>
       <c r="H42">
-        <v>-0.3002315629515806</v>
+        <v>-0.2407478906524494</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-2.352795266528396</v>
+        <v>-2.366575175028149</v>
       </c>
       <c r="C43">
-        <v>-3.405697142448692</v>
+        <v>-2.938462910459784</v>
       </c>
       <c r="D43">
-        <v>-2.993792707007612</v>
+        <v>-2.696710328885216</v>
       </c>
       <c r="E43">
-        <v>-2.192837773885542</v>
+        <v>-1.95069364575147</v>
       </c>
       <c r="F43">
-        <v>-0.9778007494416234</v>
+        <v>-0.7392224733595938</v>
       </c>
       <c r="G43">
-        <v>0.3842213349612277</v>
+        <v>-0.07919076264757538</v>
       </c>
       <c r="H43">
-        <v>2.309265818604717</v>
+        <v>2.22570004498017</v>
       </c>
     </row>
     <row r="44" spans="1:8">
